--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -306,12 +306,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1260,7 +1260,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <f>E6+1</f>
+        <f t="shared" ref="D7:D15" si="0">E6+1</f>
         <v>201</v>
       </c>
       <c r="E7" s="1">
@@ -1287,7 +1287,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <f>E7+1</f>
+        <f t="shared" si="0"/>
         <v>401</v>
       </c>
       <c r="E8" s="1">
@@ -1320,7 +1320,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="1">
-        <f>E8+1</f>
+        <f t="shared" si="0"/>
         <v>601</v>
       </c>
       <c r="E9" s="1">
@@ -1350,7 +1350,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="1">
-        <f>E9+1</f>
+        <f t="shared" si="0"/>
         <v>801</v>
       </c>
       <c r="E10" s="1">
@@ -1380,7 +1380,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="1">
-        <f>E10+1</f>
+        <f t="shared" si="0"/>
         <v>1001</v>
       </c>
       <c r="E11" s="1">
@@ -1410,7 +1410,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="1">
-        <f>E11+1</f>
+        <f t="shared" si="0"/>
         <v>601</v>
       </c>
       <c r="E12" s="1">
@@ -1440,7 +1440,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="1">
-        <f>E12+1</f>
+        <f t="shared" si="0"/>
         <v>701</v>
       </c>
       <c r="E13" s="1">
@@ -1470,7 +1470,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="1">
-        <f>E13+1</f>
+        <f t="shared" si="0"/>
         <v>801</v>
       </c>
       <c r="E14" s="1">
@@ -1500,7 +1500,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="1">
-        <f>E14+1</f>
+        <f t="shared" si="0"/>
         <v>901</v>
       </c>
       <c r="E15" s="1">
@@ -1619,7 +1619,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H3 I3 C4:E4 F4 G4 H4 I4 C5:G5 H5 I5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5 F3:I5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -306,12 +306,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1619,7 +1619,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5 F3:I5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:I5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -102,7 +102,7 @@
     <t>5001,5002,11,5003</t>
   </si>
   <si>
-    <t>100,20,100,1</t>
+    <t>300,60,50,1</t>
   </si>
   <si>
     <t>1,5,10,20</t>
@@ -114,13 +114,13 @@
     <t>5001,5002,12,5003</t>
   </si>
   <si>
-    <t>110,25,1,1</t>
+    <t>600,120,100,1</t>
   </si>
   <si>
     <t>铜矿石，黑铁矿，珍品材料，皮肤精华</t>
   </si>
   <si>
-    <t>120,30,120,1</t>
+    <t>1000,500,200,1</t>
   </si>
   <si>
     <t>#</t>

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -102,7 +102,7 @@
     <t>5001,5002,11,5003</t>
   </si>
   <si>
-    <t>300,60,50,1</t>
+    <t>300,150,50,1</t>
   </si>
   <si>
     <t>1,5,10,20</t>
@@ -114,13 +114,13 @@
     <t>5001,5002,12,5003</t>
   </si>
   <si>
-    <t>600,120,100,1</t>
+    <t>600,300,1,1</t>
   </si>
   <si>
     <t>铜矿石，黑铁矿，珍品材料，皮肤精华</t>
   </si>
   <si>
-    <t>1000,500,200,1</t>
+    <t>1000,500,100,1</t>
   </si>
   <si>
     <t>#</t>

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -102,7 +102,7 @@
     <t>5001,5002,11,5003</t>
   </si>
   <si>
-    <t>300,150,50,1</t>
+    <t>300,50,10,1</t>
   </si>
   <si>
     <t>1,5,10,20</t>
@@ -114,13 +114,13 @@
     <t>5001,5002,12,5003</t>
   </si>
   <si>
-    <t>600,300,1,1</t>
+    <t>600,100,1,1</t>
   </si>
   <si>
     <t>铜矿石，黑铁矿，珍品材料，皮肤精华</t>
   </si>
   <si>
-    <t>1000,500,100,1</t>
+    <t>1000,150,20,1</t>
   </si>
   <si>
     <t>#</t>

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="23">
   <si>
     <t>ID</t>
   </si>
@@ -121,6 +121,12 @@
   </si>
   <si>
     <t>1000,150,20,1</t>
+  </si>
+  <si>
+    <t>1500,200,1,1</t>
+  </si>
+  <si>
+    <t>2000,250,30,1</t>
   </si>
   <si>
     <t>#</t>
@@ -1310,12 +1316,6 @@
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1326,26 +1326,23 @@
       <c r="E9" s="1">
         <v>800</v>
       </c>
-      <c r="F9" s="1">
-        <v>5</v>
-      </c>
-      <c r="G9" s="1">
-        <v>4001</v>
-      </c>
-      <c r="H9" s="1">
-        <v>40000</v>
-      </c>
-      <c r="I9" s="1">
-        <v>40000</v>
+      <c r="F9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1356,25 +1353,28 @@
       <c r="E10" s="1">
         <v>1000</v>
       </c>
-      <c r="F10" s="1">
-        <v>5</v>
-      </c>
-      <c r="G10" s="5">
-        <v>4002</v>
-      </c>
-      <c r="H10" s="1">
-        <v>600000</v>
-      </c>
-      <c r="I10" s="1">
-        <v>600000</v>
+      <c r="F10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C11" s="1">
         <v>6</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C12" s="1">
         <v>7</v>
@@ -1431,10 +1431,10 @@
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C13" s="1">
         <v>8</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C14" s="1">
         <v>9</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C15" s="1">
         <v>10</v>

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -61,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="30">
   <si>
     <t>ID</t>
   </si>
@@ -129,7 +134,28 @@
     <t>2000,250,30,1</t>
   </si>
   <si>
-    <t>#</t>
+    <t>5,5,5,5</t>
+  </si>
+  <si>
+    <t>5001,5002,5019,5003</t>
+  </si>
+  <si>
+    <t>3000,300,1,1</t>
+  </si>
+  <si>
+    <t>铜矿石，黑铁矿，5阶神兵符，皮肤精华</t>
+  </si>
+  <si>
+    <t>4000,350,30,1</t>
+  </si>
+  <si>
+    <t>5000,400,1,1</t>
+  </si>
+  <si>
+    <t>6000,450,30,1</t>
+  </si>
+  <si>
+    <t>7000,500,1,1</t>
   </si>
 </sst>
 </file>
@@ -1370,12 +1396,6 @@
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1384,139 +1404,130 @@
         <v>1001</v>
       </c>
       <c r="E11" s="1">
-        <v>600</v>
-      </c>
-      <c r="F11" s="1">
-        <v>5</v>
-      </c>
-      <c r="G11" s="1">
-        <v>4001</v>
-      </c>
-      <c r="H11" s="1">
-        <v>60000</v>
-      </c>
-      <c r="I11" s="1">
-        <v>60000</v>
+        <v>1200</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1">
         <f t="shared" si="0"/>
-        <v>601</v>
+        <v>1201</v>
       </c>
       <c r="E12" s="1">
-        <v>700</v>
-      </c>
-      <c r="F12" s="1">
-        <v>5</v>
-      </c>
-      <c r="G12" s="5">
-        <v>4002</v>
-      </c>
-      <c r="H12" s="1">
-        <v>800000</v>
-      </c>
-      <c r="I12" s="1">
-        <v>800000</v>
+        <v>1400</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1">
         <f t="shared" si="0"/>
-        <v>701</v>
+        <v>1401</v>
       </c>
       <c r="E13" s="1">
-        <v>800</v>
-      </c>
-      <c r="F13" s="1">
-        <v>5</v>
-      </c>
-      <c r="G13" s="1">
-        <v>4001</v>
-      </c>
-      <c r="H13" s="1">
-        <v>80000</v>
-      </c>
-      <c r="I13" s="1">
-        <v>80000</v>
+        <v>1600</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="1">
         <f t="shared" si="0"/>
-        <v>801</v>
+        <v>1601</v>
       </c>
       <c r="E14" s="1">
-        <v>900</v>
-      </c>
-      <c r="F14" s="1">
-        <v>5</v>
-      </c>
-      <c r="G14" s="1">
-        <v>4001</v>
-      </c>
-      <c r="H14" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="I14" s="1">
-        <v>1000000</v>
+        <v>1800</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="1">
         <f t="shared" si="0"/>
-        <v>901</v>
+        <v>1801</v>
       </c>
       <c r="E15" s="1">
-        <v>1000</v>
-      </c>
-      <c r="F15" s="1">
-        <v>5</v>
-      </c>
-      <c r="G15" s="1">
-        <v>4001</v>
-      </c>
-      <c r="H15" s="1">
-        <v>100000</v>
-      </c>
-      <c r="I15" s="1">
-        <v>100000</v>
+        <v>2000</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1"/>

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -146,13 +146,13 @@
     <t>铜矿石，黑铁矿，5阶神兵符，皮肤精华</t>
   </si>
   <si>
-    <t>4000,350,30,1</t>
+    <t>4000,350,3,1</t>
   </si>
   <si>
     <t>5000,400,1,1</t>
   </si>
   <si>
-    <t>6000,450,30,1</t>
+    <t>6000,450,3,1</t>
   </si>
   <si>
     <t>7000,500,1,1</t>

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="31">
   <si>
     <t>ID</t>
   </si>
@@ -146,13 +146,16 @@
     <t>铜矿石，黑铁矿，5阶神兵符，皮肤精华</t>
   </si>
   <si>
-    <t>4000,350,3,1</t>
+    <t>5001,5002,13,5003</t>
+  </si>
+  <si>
+    <t>4000,350,2,1</t>
   </si>
   <si>
     <t>5000,400,1,1</t>
   </si>
   <si>
-    <t>6000,450,3,1</t>
+    <t>6000,450,2,1</t>
   </si>
   <si>
     <t>7000,500,1,1</t>
@@ -338,12 +341,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1437,10 +1440,10 @@
         <v>11</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>14</v>
@@ -1467,7 +1470,7 @@
         <v>23</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>14</v>
@@ -1491,10 +1494,10 @@
         <v>11</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>14</v>
@@ -1521,7 +1524,7 @@
         <v>23</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>14</v>
